--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SR24"/>
+  <dimension ref="A1:SS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2977,6 +2977,11 @@
           <t>Price_2026-09-05 11:45</t>
         </is>
       </c>
+      <c r="SS1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-06 12:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5535,6 +5540,11 @@
         </is>
       </c>
       <c r="SR2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SS2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7937,6 +7947,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SS3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10375,6 +10390,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SS4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12937,6 +12957,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SS5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15499,6 +15524,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="SS6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18061,6 +18091,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SS7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20623,6 +20658,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SS8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23185,6 +23225,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SS9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25747,6 +25792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SS10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28309,6 +28359,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SS11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30871,6 +30926,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SS12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33433,6 +33493,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SS13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35995,6 +36060,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SS14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38553,6 +38623,11 @@
         </is>
       </c>
       <c r="SR15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SS15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40519,6 +40594,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SS16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43081,6 +43161,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SS17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45643,6 +45728,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SS18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48205,6 +48295,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SS19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50767,6 +50862,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SS20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53329,6 +53429,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SS21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55889,6 +55994,11 @@
       <c r="SR22" t="inlineStr">
         <is>
           <t>3.879</t>
+        </is>
+      </c>
+      <c r="SS22" t="inlineStr">
+        <is>
+          <t>3.799</t>
         </is>
       </c>
     </row>
@@ -58461,6 +58571,11 @@
         </is>
       </c>
       <c r="SR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SS23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60795,6 +60910,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SS24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SS24"/>
+  <dimension ref="A1:ST24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2982,6 +2982,11 @@
           <t>Price_2026-09-06 12:05</t>
         </is>
       </c>
+      <c r="ST1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-07 14:06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5545,6 +5550,11 @@
         </is>
       </c>
       <c r="SS2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="ST2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7952,6 +7962,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="ST3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10395,6 +10410,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="ST4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12962,6 +12982,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="ST5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15529,6 +15554,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="ST6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18096,6 +18126,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="ST7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20663,6 +20698,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="ST8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23230,6 +23270,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="ST9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25797,6 +25842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="ST10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28364,6 +28414,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="ST11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30931,6 +30986,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="ST12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33498,6 +33558,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="ST13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36065,6 +36130,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="ST14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38628,6 +38698,11 @@
         </is>
       </c>
       <c r="SS15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="ST15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40599,6 +40674,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="ST16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43166,6 +43246,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="ST17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45733,6 +45818,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="ST18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48300,6 +48390,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="ST19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50867,6 +50962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="ST20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53434,6 +53534,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="ST21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55999,6 +56104,11 @@
       <c r="SS22" t="inlineStr">
         <is>
           <t>3.799</t>
+        </is>
+      </c>
+      <c r="ST22" t="inlineStr">
+        <is>
+          <t>3.749</t>
         </is>
       </c>
     </row>
@@ -58576,6 +58686,11 @@
         </is>
       </c>
       <c r="SS23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="ST23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60915,6 +61030,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="ST24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ST24"/>
+  <dimension ref="A1:SU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2987,6 +2987,11 @@
           <t>Price_2026-09-07 14:06</t>
         </is>
       </c>
+      <c r="SU1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-08 12:46</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5555,6 +5560,11 @@
         </is>
       </c>
       <c r="ST2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SU2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7967,6 +7977,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SU3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10415,6 +10430,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SU4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12987,6 +13007,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SU5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15559,6 +15584,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18131,6 +18161,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SU7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20703,6 +20738,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SU8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23275,6 +23315,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SU9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25847,6 +25892,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SU10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28419,6 +28469,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SU11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30991,6 +31046,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SU12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33563,6 +33623,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SU13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36135,6 +36200,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SU14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38705,6 +38775,11 @@
       <c r="ST15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SU15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -40679,6 +40754,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SU16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43251,6 +43331,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SU17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45823,6 +45908,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SU18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48395,6 +48485,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SU19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50967,6 +51062,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SU20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53539,6 +53639,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SU21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56109,6 +56214,11 @@
       <c r="ST22" t="inlineStr">
         <is>
           <t>3.749</t>
+        </is>
+      </c>
+      <c r="SU22" t="inlineStr">
+        <is>
+          <t>4.199</t>
         </is>
       </c>
     </row>
@@ -58691,6 +58801,11 @@
         </is>
       </c>
       <c r="ST23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SU23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61035,6 +61150,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SU24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SU24"/>
+  <dimension ref="A1:SV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2992,6 +2992,11 @@
           <t>Price_2026-09-08 12:46</t>
         </is>
       </c>
+      <c r="SV1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-09 12:52</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5565,6 +5570,11 @@
         </is>
       </c>
       <c r="SU2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SV2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7982,6 +7992,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10435,6 +10450,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13012,6 +13032,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SV5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15589,6 +15614,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SV6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18166,6 +18196,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="SV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20743,6 +20778,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SV8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23320,6 +23360,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="SV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25897,6 +25942,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="SV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28474,6 +28524,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="SV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31051,6 +31106,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="SV12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33628,6 +33688,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="SV13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36205,6 +36270,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SV14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38780,6 +38850,11 @@
       <c r="SU15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="SV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -40759,6 +40834,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SV16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43336,6 +43416,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SV17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45913,6 +45998,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48490,6 +48580,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SV19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51067,6 +51162,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SV20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53644,6 +53744,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="SV21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56217,6 +56322,11 @@
         </is>
       </c>
       <c r="SU22" t="inlineStr">
+        <is>
+          <t>4.199</t>
+        </is>
+      </c>
+      <c r="SV22" t="inlineStr">
         <is>
           <t>4.199</t>
         </is>
@@ -58806,6 +58916,11 @@
         </is>
       </c>
       <c r="SU23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SV23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61155,6 +61270,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SV24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SV24"/>
+  <dimension ref="A1:SW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2997,6 +2997,11 @@
           <t>Price_2026-09-09 12:52</t>
         </is>
       </c>
+      <c r="SW1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-10 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5575,6 +5580,11 @@
         </is>
       </c>
       <c r="SV2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SW2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7997,6 +8007,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10455,6 +10470,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13037,6 +13057,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SW5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15619,6 +15644,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18201,6 +18231,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20783,6 +20818,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SW8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23365,6 +23405,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25947,6 +25992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28529,6 +28579,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31111,6 +31166,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SW12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33693,6 +33753,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SW13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36275,6 +36340,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SW14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38853,6 +38923,11 @@
         </is>
       </c>
       <c r="SV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40839,6 +40914,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SW16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43421,6 +43501,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SW17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46003,6 +46088,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48585,6 +48675,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SW19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51167,6 +51262,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SW20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53749,6 +53849,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SW21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56327,6 +56432,11 @@
         </is>
       </c>
       <c r="SV22" t="inlineStr">
+        <is>
+          <t>4.199</t>
+        </is>
+      </c>
+      <c r="SW22" t="inlineStr">
         <is>
           <t>4.199</t>
         </is>
@@ -58921,6 +59031,11 @@
         </is>
       </c>
       <c r="SV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SW23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61275,6 +61390,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SW24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SW24"/>
+  <dimension ref="A1:SX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3002,6 +3002,11 @@
           <t>Price_2026-09-10 12:51</t>
         </is>
       </c>
+      <c r="SX1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-11 12:44</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5585,6 +5590,11 @@
         </is>
       </c>
       <c r="SW2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SX2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8012,6 +8022,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SX3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10475,6 +10490,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SX4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13062,6 +13082,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SX5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15649,6 +15674,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SX6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18236,6 +18266,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SX7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20823,6 +20858,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SX8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23410,6 +23450,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SX9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25997,6 +26042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SX10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28584,6 +28634,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SX11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31171,6 +31226,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SX12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33758,6 +33818,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SX13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36345,6 +36410,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SX14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38928,6 +38998,11 @@
         </is>
       </c>
       <c r="SW15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SX15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40919,6 +40994,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SX16" t="inlineStr">
+        <is>
+          <t>$9.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43506,6 +43586,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SX17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46093,6 +46178,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SX18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48680,6 +48770,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SX19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51267,6 +51362,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SX20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53854,6 +53954,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SX21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56437,6 +56542,11 @@
         </is>
       </c>
       <c r="SW22" t="inlineStr">
+        <is>
+          <t>4.199</t>
+        </is>
+      </c>
+      <c r="SX22" t="inlineStr">
         <is>
           <t>4.199</t>
         </is>
@@ -59036,6 +59146,11 @@
         </is>
       </c>
       <c r="SW23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SX23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61395,6 +61510,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SX24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SX24"/>
+  <dimension ref="A1:SY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3007,6 +3007,11 @@
           <t>Price_2026-09-11 12:44</t>
         </is>
       </c>
+      <c r="SY1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-12 12:07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5595,6 +5600,11 @@
         </is>
       </c>
       <c r="SX2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SY2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8027,6 +8037,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SY3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10495,6 +10510,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SY4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13087,6 +13107,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SY5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15679,6 +15704,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18271,6 +18301,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SY7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20863,6 +20898,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SY8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23455,6 +23495,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SY9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26047,6 +26092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SY10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28639,6 +28689,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SY11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31231,6 +31286,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SY12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33823,6 +33883,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SY13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36415,6 +36480,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SY14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39003,6 +39073,11 @@
         </is>
       </c>
       <c r="SX15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SY15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40999,6 +41074,11 @@
           <t>$9.99</t>
         </is>
       </c>
+      <c r="SY16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43591,6 +43671,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SY17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46183,6 +46268,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SY18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48775,6 +48865,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SY19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51367,6 +51462,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SY20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53959,6 +54059,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SY21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56549,6 +56654,11 @@
       <c r="SX22" t="inlineStr">
         <is>
           <t>4.199</t>
+        </is>
+      </c>
+      <c r="SY22" t="inlineStr">
+        <is>
+          <t>4.149</t>
         </is>
       </c>
     </row>
@@ -59151,6 +59261,11 @@
         </is>
       </c>
       <c r="SX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SY23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61515,6 +61630,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SY24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SY24"/>
+  <dimension ref="A1:SZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3012,6 +3012,11 @@
           <t>Price_2026-09-12 12:07</t>
         </is>
       </c>
+      <c r="SZ1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-13 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5605,6 +5610,11 @@
         </is>
       </c>
       <c r="SY2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SZ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8042,6 +8052,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SZ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10515,6 +10530,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SZ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13112,6 +13132,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SZ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15709,6 +15734,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SZ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18306,6 +18336,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SZ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20903,6 +20938,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SZ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23500,6 +23540,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SZ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26097,6 +26142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SZ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28694,6 +28744,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SZ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31291,6 +31346,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SZ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33888,6 +33948,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SZ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36485,6 +36550,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SZ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39078,6 +39148,11 @@
         </is>
       </c>
       <c r="SY15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SZ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41079,6 +41154,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SZ16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43676,6 +43756,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SZ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46273,6 +46358,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SZ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48870,6 +48960,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SZ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51467,6 +51562,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SZ20" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54064,6 +54164,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SZ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56659,6 +56764,11 @@
       <c r="SY22" t="inlineStr">
         <is>
           <t>4.149</t>
+        </is>
+      </c>
+      <c r="SZ22" t="inlineStr">
+        <is>
+          <t>4.099</t>
         </is>
       </c>
     </row>
@@ -59266,6 +59376,11 @@
         </is>
       </c>
       <c r="SY23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SZ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61635,6 +61750,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SZ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SZ24"/>
+  <dimension ref="A1:TA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3017,6 +3017,11 @@
           <t>Price_2026-09-13 13:15</t>
         </is>
       </c>
+      <c r="TA1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-14 14:52</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5615,6 +5620,11 @@
         </is>
       </c>
       <c r="SZ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TA2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8057,6 +8067,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TA3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10535,6 +10550,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TA4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13137,6 +13157,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TA5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15739,6 +15764,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TA6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18341,6 +18371,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TA7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20943,6 +20978,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TA8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23545,6 +23585,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TA9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26147,6 +26192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TA10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28749,6 +28799,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TA11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31351,6 +31406,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TA12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33953,6 +34013,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TA13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36555,6 +36620,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TA14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39153,6 +39223,11 @@
         </is>
       </c>
       <c r="SZ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TA15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41159,6 +41234,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TA16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43761,6 +43841,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TA17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46363,6 +46448,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TA18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48965,6 +49055,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TA19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51567,6 +51662,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TA20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54169,6 +54269,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TA21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56767,6 +56872,11 @@
         </is>
       </c>
       <c r="SZ22" t="inlineStr">
+        <is>
+          <t>4.099</t>
+        </is>
+      </c>
+      <c r="TA22" t="inlineStr">
         <is>
           <t>4.099</t>
         </is>
@@ -59381,6 +59491,11 @@
         </is>
       </c>
       <c r="SZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TA23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61755,6 +61870,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TA24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TA24"/>
+  <dimension ref="A1:TB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3022,6 +3022,11 @@
           <t>Price_2026-09-14 14:52</t>
         </is>
       </c>
+      <c r="TB1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-15 13:16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5625,6 +5630,11 @@
         </is>
       </c>
       <c r="TA2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TB2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8072,6 +8082,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TB3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10555,6 +10570,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TB4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13162,6 +13182,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TB5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15769,6 +15794,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TB6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18376,6 +18406,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TB7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20983,6 +21018,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TB8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23590,6 +23630,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TB9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26197,6 +26242,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TB10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28804,6 +28854,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TB11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31411,6 +31466,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TB12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34018,6 +34078,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TB13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36625,6 +36690,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TB14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39228,6 +39298,11 @@
         </is>
       </c>
       <c r="TA15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TB15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41239,6 +41314,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TB16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43846,6 +43926,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TB17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46453,6 +46538,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TB18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49060,6 +49150,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TB19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51667,6 +51762,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TB20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54274,6 +54374,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TB21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56877,6 +56982,11 @@
         </is>
       </c>
       <c r="TA22" t="inlineStr">
+        <is>
+          <t>4.099</t>
+        </is>
+      </c>
+      <c r="TB22" t="inlineStr">
         <is>
           <t>4.099</t>
         </is>
@@ -59496,6 +59606,11 @@
         </is>
       </c>
       <c r="TA23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TB23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61875,6 +61990,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TB24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TB24"/>
+  <dimension ref="A1:TC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3027,6 +3027,11 @@
           <t>Price_2026-09-15 13:16</t>
         </is>
       </c>
+      <c r="TC1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-16 13:14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5635,6 +5640,11 @@
         </is>
       </c>
       <c r="TB2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TC2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8087,6 +8097,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TC3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10575,6 +10590,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TC4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13187,6 +13207,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TC5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15799,6 +15824,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TC6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18411,6 +18441,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TC7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21023,6 +21058,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TC8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23635,6 +23675,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TC9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26247,6 +26292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TC10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28859,6 +28909,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TC11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31471,6 +31526,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TC12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34083,6 +34143,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TC13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36695,6 +36760,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TC14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39303,6 +39373,11 @@
         </is>
       </c>
       <c r="TB15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TC15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41319,6 +41394,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TC16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43931,6 +44011,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TC17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46543,6 +46628,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TC18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49155,6 +49245,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TC19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51767,6 +51862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TC20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54379,6 +54479,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TC21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -56989,6 +57094,11 @@
       <c r="TB22" t="inlineStr">
         <is>
           <t>4.099</t>
+        </is>
+      </c>
+      <c r="TC22" t="inlineStr">
+        <is>
+          <t>4.449</t>
         </is>
       </c>
     </row>
@@ -59611,6 +59721,11 @@
         </is>
       </c>
       <c r="TB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TC23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -61995,6 +62110,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TC24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TC24"/>
+  <dimension ref="A1:TD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3032,6 +3032,11 @@
           <t>Price_2026-09-16 13:14</t>
         </is>
       </c>
+      <c r="TD1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-17 13:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5645,6 +5650,11 @@
         </is>
       </c>
       <c r="TC2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TD2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8102,6 +8112,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TD3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10595,6 +10610,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TD4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13212,6 +13232,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TD5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15829,6 +15854,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TD6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18446,6 +18476,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TD7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21063,6 +21098,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TD8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23680,6 +23720,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TD9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26297,6 +26342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TD10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28914,6 +28964,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TD11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31531,6 +31586,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TD12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34148,6 +34208,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TD13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36765,6 +36830,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TD14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39378,6 +39448,11 @@
         </is>
       </c>
       <c r="TC15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TD15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41399,6 +41474,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TD16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44016,6 +44096,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TD17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46633,6 +46718,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TD18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49250,6 +49340,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TD19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51867,6 +51962,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TD20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54484,6 +54584,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TD21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57097,6 +57202,11 @@
         </is>
       </c>
       <c r="TC22" t="inlineStr">
+        <is>
+          <t>4.449</t>
+        </is>
+      </c>
+      <c r="TD22" t="inlineStr">
         <is>
           <t>4.449</t>
         </is>
@@ -59726,6 +59836,11 @@
         </is>
       </c>
       <c r="TC23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TD23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62115,6 +62230,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TD24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TD24"/>
+  <dimension ref="A1:TE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,6 +3037,11 @@
           <t>Price_2026-09-17 13:11</t>
         </is>
       </c>
+      <c r="TE1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-18 12:50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5655,6 +5660,11 @@
         </is>
       </c>
       <c r="TD2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TE2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8117,6 +8127,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TE3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10615,6 +10630,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TE4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13237,6 +13257,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TE5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15859,6 +15884,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TE6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18481,6 +18511,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TE7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21103,6 +21138,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TE8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23725,6 +23765,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TE9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26347,6 +26392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TE10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28969,6 +29019,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TE11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31591,6 +31646,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TE12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34213,6 +34273,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TE13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36835,6 +36900,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TE14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39453,6 +39523,11 @@
         </is>
       </c>
       <c r="TD15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TE15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41479,6 +41554,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TE16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44101,6 +44181,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TE17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46723,6 +46808,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TE18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49345,6 +49435,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TE19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51967,6 +52062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TE20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54589,6 +54689,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TE21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57209,6 +57314,11 @@
       <c r="TD22" t="inlineStr">
         <is>
           <t>4.449</t>
+        </is>
+      </c>
+      <c r="TE22" t="inlineStr">
+        <is>
+          <t>4.399</t>
         </is>
       </c>
     </row>
@@ -59841,6 +59951,11 @@
         </is>
       </c>
       <c r="TD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TE23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62235,6 +62350,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TE24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TE24"/>
+  <dimension ref="A1:TF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,6 +3042,11 @@
           <t>Price_2026-09-18 12:50</t>
         </is>
       </c>
+      <c r="TF1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-19 02:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5665,6 +5670,11 @@
         </is>
       </c>
       <c r="TE2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TF2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8132,6 +8142,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TF3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10635,6 +10650,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TF4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13262,6 +13282,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TF5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15889,6 +15914,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TF6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18516,6 +18546,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TF7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21143,6 +21178,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TF8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23770,6 +23810,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TF9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26397,6 +26442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TF10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29024,6 +29074,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TF11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31651,6 +31706,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TF12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34278,6 +34338,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TF13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36905,6 +36970,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TF14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39528,6 +39598,11 @@
         </is>
       </c>
       <c r="TE15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TF15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41559,6 +41634,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TF16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44186,6 +44266,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TF17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46813,6 +46898,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TF18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49440,6 +49530,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TF19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52067,6 +52162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TF20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54694,6 +54794,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TF21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57317,6 +57422,11 @@
         </is>
       </c>
       <c r="TE22" t="inlineStr">
+        <is>
+          <t>4.399</t>
+        </is>
+      </c>
+      <c r="TF22" t="inlineStr">
         <is>
           <t>4.399</t>
         </is>
@@ -59956,6 +60066,11 @@
         </is>
       </c>
       <c r="TE23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TF23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62355,6 +62470,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TF24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TF24"/>
+  <dimension ref="A1:TG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3047,6 +3047,11 @@
           <t>Price_2026-09-19 02:29</t>
         </is>
       </c>
+      <c r="TG1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-19 12:26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5675,6 +5680,11 @@
         </is>
       </c>
       <c r="TF2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TG2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8147,6 +8157,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TG3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10655,6 +10670,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TG4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13287,6 +13307,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TG5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15919,6 +15944,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TG6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18551,6 +18581,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TG7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21183,6 +21218,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TG8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23815,6 +23855,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TG9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26447,6 +26492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TG10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29079,6 +29129,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TG11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31711,6 +31766,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TG12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34343,6 +34403,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TG13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -36975,6 +37040,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TG14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39603,6 +39673,11 @@
         </is>
       </c>
       <c r="TF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TG15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41639,6 +41714,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TG16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44271,6 +44351,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TG17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46903,6 +46988,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TG18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49535,6 +49625,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TG19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52167,6 +52262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TG20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54799,6 +54899,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TG21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57427,6 +57532,11 @@
         </is>
       </c>
       <c r="TF22" t="inlineStr">
+        <is>
+          <t>4.399</t>
+        </is>
+      </c>
+      <c r="TG22" t="inlineStr">
         <is>
           <t>4.399</t>
         </is>
@@ -60071,6 +60181,11 @@
         </is>
       </c>
       <c r="TF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TG23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62475,6 +62590,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TG24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TG24"/>
+  <dimension ref="A1:TH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3052,6 +3052,11 @@
           <t>Price_2026-09-19 12:26</t>
         </is>
       </c>
+      <c r="TH1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-20 13:01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5685,6 +5690,11 @@
         </is>
       </c>
       <c r="TG2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TH2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8162,6 +8172,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TH3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10675,6 +10690,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TH4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13312,6 +13332,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TH5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15949,6 +15974,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TH6" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18586,6 +18616,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TH7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21223,6 +21258,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TH8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23860,6 +23900,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TH9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26497,6 +26542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TH10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29134,6 +29184,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TH11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31771,6 +31826,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TH12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34408,6 +34468,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TH13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37045,6 +37110,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TH14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39680,6 +39750,11 @@
       <c r="TG15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TH15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -41719,6 +41794,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TH16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44356,6 +44436,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TH17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46993,6 +47078,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TH18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49630,6 +49720,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TH19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52267,6 +52362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TH20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -54904,6 +55004,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TH21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57539,6 +57644,11 @@
       <c r="TG22" t="inlineStr">
         <is>
           <t>4.399</t>
+        </is>
+      </c>
+      <c r="TH22" t="inlineStr">
+        <is>
+          <t>4.349</t>
         </is>
       </c>
     </row>
@@ -60186,6 +60296,11 @@
         </is>
       </c>
       <c r="TG23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TH23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62595,6 +62710,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TH24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TH24"/>
+  <dimension ref="A1:TI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3057,6 +3057,11 @@
           <t>Price_2026-09-20 13:01</t>
         </is>
       </c>
+      <c r="TI1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-21 15:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5695,6 +5700,11 @@
         </is>
       </c>
       <c r="TH2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TI2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8177,6 +8187,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TI3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10695,6 +10710,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TI4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13337,6 +13357,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TI5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15979,6 +16004,11 @@
           <t>$3.49</t>
         </is>
       </c>
+      <c r="TI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18621,6 +18651,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="TI7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21263,6 +21298,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TI8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23905,6 +23945,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="TI9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26547,6 +26592,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="TI10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29189,6 +29239,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="TI11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31831,6 +31886,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TI12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34473,6 +34533,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="TI13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37115,6 +37180,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TI14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39755,6 +39825,11 @@
       <c r="TH15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="TI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -41799,6 +41874,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TI16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44441,6 +44521,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TI17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47083,6 +47168,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TI18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49725,6 +49815,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="TI19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52367,6 +52462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TI20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55009,6 +55109,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="TI21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57647,6 +57752,11 @@
         </is>
       </c>
       <c r="TH22" t="inlineStr">
+        <is>
+          <t>4.349</t>
+        </is>
+      </c>
+      <c r="TI22" t="inlineStr">
         <is>
           <t>4.349</t>
         </is>
@@ -60301,6 +60411,11 @@
         </is>
       </c>
       <c r="TH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TI23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62715,6 +62830,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TI24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TI24"/>
+  <dimension ref="A1:TJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3062,6 +3062,11 @@
           <t>Price_2026-09-21 15:00</t>
         </is>
       </c>
+      <c r="TJ1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-22 02:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5705,6 +5710,11 @@
         </is>
       </c>
       <c r="TI2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TJ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8192,6 +8202,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TJ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10715,6 +10730,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TJ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13362,6 +13382,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TJ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16009,6 +16034,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TJ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18656,6 +18686,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TJ7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21303,6 +21338,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TJ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23950,6 +23990,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TJ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26597,6 +26642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TJ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29244,6 +29294,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TJ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31891,6 +31946,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TJ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34538,6 +34598,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TJ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37185,6 +37250,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TJ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39828,6 +39898,11 @@
         </is>
       </c>
       <c r="TI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41879,6 +41954,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TJ16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44526,6 +44606,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TJ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47173,6 +47258,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TJ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49820,6 +49910,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TJ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52467,6 +52562,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TJ20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55114,6 +55214,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TJ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57757,6 +57862,11 @@
         </is>
       </c>
       <c r="TI22" t="inlineStr">
+        <is>
+          <t>4.349</t>
+        </is>
+      </c>
+      <c r="TJ22" t="inlineStr">
         <is>
           <t>4.349</t>
         </is>
@@ -60416,6 +60526,11 @@
         </is>
       </c>
       <c r="TI23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TJ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62835,6 +62950,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TJ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TJ24"/>
+  <dimension ref="A1:TK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3067,6 +3067,11 @@
           <t>Price_2026-09-22 02:30</t>
         </is>
       </c>
+      <c r="TK1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-22 02:51</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5715,6 +5720,11 @@
         </is>
       </c>
       <c r="TJ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TK2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8207,6 +8217,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TK3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10735,6 +10750,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TK4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13387,6 +13407,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TK5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16039,6 +16064,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18691,6 +18721,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TK7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21343,6 +21378,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TK8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23995,6 +24035,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TK9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26647,6 +26692,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TK10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29299,6 +29349,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TK11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31951,6 +32006,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TK12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34603,6 +34663,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TK13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37255,6 +37320,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TK14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39903,6 +39973,11 @@
         </is>
       </c>
       <c r="TJ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TK15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -41959,6 +42034,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TK16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44611,6 +44691,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TK17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47263,6 +47348,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TK18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -49915,6 +50005,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TK19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52567,6 +52662,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TK20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55219,6 +55319,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TK21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57867,6 +57972,11 @@
         </is>
       </c>
       <c r="TJ22" t="inlineStr">
+        <is>
+          <t>4.349</t>
+        </is>
+      </c>
+      <c r="TK22" t="inlineStr">
         <is>
           <t>4.349</t>
         </is>
@@ -60531,6 +60641,11 @@
         </is>
       </c>
       <c r="TJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TK23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -62955,6 +63070,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TK24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TK24"/>
+  <dimension ref="A1:TL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3072,6 +3072,11 @@
           <t>Price_2026-09-22 02:51</t>
         </is>
       </c>
+      <c r="TL1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-22 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5725,6 +5730,11 @@
         </is>
       </c>
       <c r="TK2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TL2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8222,6 +8232,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TL3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10755,6 +10770,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TL4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13412,6 +13432,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TL5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16069,6 +16094,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TL6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18726,6 +18756,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TL7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21383,6 +21418,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TL8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24040,6 +24080,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TL9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26697,6 +26742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TL10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29354,6 +29404,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TL11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32011,6 +32066,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TL12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34668,6 +34728,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TL13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37325,6 +37390,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TL14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39978,6 +40048,11 @@
         </is>
       </c>
       <c r="TK15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TL15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42039,6 +42114,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TL16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44696,6 +44776,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TL17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47353,6 +47438,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TL18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50010,6 +50100,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TL19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52667,6 +52762,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TL20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55324,6 +55424,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TL21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -57977,6 +58082,11 @@
         </is>
       </c>
       <c r="TK22" t="inlineStr">
+        <is>
+          <t>4.349</t>
+        </is>
+      </c>
+      <c r="TL22" t="inlineStr">
         <is>
           <t>4.349</t>
         </is>
@@ -60646,6 +60756,11 @@
         </is>
       </c>
       <c r="TK23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TL23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63075,6 +63190,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TL24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TL24"/>
+  <dimension ref="A1:TM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,11 @@
           <t>Price_2026-09-22 13:15</t>
         </is>
       </c>
+      <c r="TM1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-23 13:31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5735,6 +5740,11 @@
         </is>
       </c>
       <c r="TL2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TM2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8237,6 +8247,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TM3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10775,6 +10790,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TM4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13437,6 +13457,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TM5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16099,6 +16124,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18761,6 +18791,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TM7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21423,6 +21458,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TM8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24085,6 +24125,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TM9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26747,6 +26792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TM10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29409,6 +29459,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TM11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32071,6 +32126,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TM12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34733,6 +34793,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TM13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37395,6 +37460,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TM14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40053,6 +40123,11 @@
         </is>
       </c>
       <c r="TL15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TM15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42119,6 +42194,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TM16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44781,6 +44861,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TM17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47443,6 +47528,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TM18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50105,6 +50195,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TM19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52767,6 +52862,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TM20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55429,6 +55529,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TM21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58089,6 +58194,11 @@
       <c r="TL22" t="inlineStr">
         <is>
           <t>4.349</t>
+        </is>
+      </c>
+      <c r="TM22" t="inlineStr">
+        <is>
+          <t>4.299</t>
         </is>
       </c>
     </row>
@@ -60761,6 +60871,11 @@
         </is>
       </c>
       <c r="TL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TM23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63195,6 +63310,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TM24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TM24"/>
+  <dimension ref="A1:TN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3082,6 +3082,11 @@
           <t>Price_2026-09-23 13:31</t>
         </is>
       </c>
+      <c r="TN1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-24 13:20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5745,6 +5750,11 @@
         </is>
       </c>
       <c r="TM2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TN2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8252,6 +8262,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TN3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10795,6 +10810,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TN4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13462,6 +13482,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TN5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16129,6 +16154,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TN6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18796,6 +18826,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TN7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21463,6 +21498,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TN8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24130,6 +24170,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TN9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26797,6 +26842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TN10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29464,6 +29514,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TN11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32131,6 +32186,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TN12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34798,6 +34858,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TN13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37465,6 +37530,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TN14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40130,6 +40200,11 @@
       <c r="TM15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TN15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -42199,6 +42274,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TN16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44866,6 +44946,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TN17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47533,6 +47618,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TN18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50200,6 +50290,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TN19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52867,6 +52962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TN20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55534,6 +55634,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TN21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58197,6 +58302,11 @@
         </is>
       </c>
       <c r="TM22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="TN22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -60876,6 +60986,11 @@
         </is>
       </c>
       <c r="TM23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TN23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63315,6 +63430,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TN24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TN24"/>
+  <dimension ref="A1:TO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3087,6 +3087,11 @@
           <t>Price_2026-09-24 13:20</t>
         </is>
       </c>
+      <c r="TO1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-25 13:25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5755,6 +5760,11 @@
         </is>
       </c>
       <c r="TN2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TO2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8267,6 +8277,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TO3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10815,6 +10830,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TO4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13487,6 +13507,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TO5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16159,6 +16184,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18831,6 +18861,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TO7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21503,6 +21538,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TO8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24175,6 +24215,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="TO9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26847,6 +26892,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="TO10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29519,6 +29569,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="TO11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32191,6 +32246,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TO12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34863,6 +34923,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="TO13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37535,6 +37600,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TO14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40203,6 +40273,11 @@
         </is>
       </c>
       <c r="TN15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
+        </is>
+      </c>
+      <c r="TO15" t="inlineStr">
         <is>
           <t>$4.49</t>
         </is>
@@ -42279,6 +42354,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TO16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44951,6 +45031,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TO17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47623,6 +47708,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TO18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50295,6 +50385,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TO19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52967,6 +53062,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TO20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55639,6 +55739,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="TO21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58307,6 +58412,11 @@
         </is>
       </c>
       <c r="TN22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="TO22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -60991,6 +61101,11 @@
         </is>
       </c>
       <c r="TN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TO23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63435,6 +63550,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TO24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TO24"/>
+  <dimension ref="A1:TP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3092,6 +3092,11 @@
           <t>Price_2026-09-25 13:25</t>
         </is>
       </c>
+      <c r="TP1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-26 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5765,6 +5770,11 @@
         </is>
       </c>
       <c r="TO2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TP2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8282,6 +8292,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TP3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10835,6 +10850,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TP4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13512,6 +13532,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TP5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16189,6 +16214,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TP6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18866,6 +18896,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TP7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21543,6 +21578,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TP8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24220,6 +24260,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="TP9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26897,6 +26942,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="TP10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29574,6 +29624,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="TP11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32251,6 +32306,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TP12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34928,6 +34988,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="TP13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37605,6 +37670,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TP14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40280,6 +40350,11 @@
       <c r="TO15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="TP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -42359,6 +42434,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TP16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45036,6 +45116,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TP17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47713,6 +47798,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TP18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50390,6 +50480,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TP19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53067,6 +53162,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TP20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55744,6 +55844,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="TP21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58417,6 +58522,11 @@
         </is>
       </c>
       <c r="TO22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="TP22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -61106,6 +61216,11 @@
         </is>
       </c>
       <c r="TO23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TP23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63555,6 +63670,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TP24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TP24"/>
+  <dimension ref="A1:TQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3097,6 +3097,11 @@
           <t>Price_2026-09-26 12:51</t>
         </is>
       </c>
+      <c r="TQ1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-27 13:42</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5775,6 +5780,11 @@
         </is>
       </c>
       <c r="TP2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TQ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8297,6 +8307,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TQ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10855,6 +10870,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TQ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13537,6 +13557,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TQ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16219,6 +16244,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18901,6 +18931,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TQ7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21583,6 +21618,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TQ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24265,6 +24305,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TQ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26947,6 +26992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TQ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29629,6 +29679,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TQ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32311,6 +32366,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="TQ12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -34993,6 +35053,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TQ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37675,6 +37740,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TQ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40353,6 +40423,11 @@
         </is>
       </c>
       <c r="TP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TQ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42439,6 +42514,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TQ16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45121,6 +45201,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TQ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47803,6 +47888,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TQ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50485,6 +50575,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TQ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53167,6 +53262,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TQ20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55849,6 +55949,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TQ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58527,6 +58632,11 @@
         </is>
       </c>
       <c r="TP22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="TQ22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -61221,6 +61331,11 @@
         </is>
       </c>
       <c r="TP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TQ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63675,6 +63790,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TQ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TQ24"/>
+  <dimension ref="A1:TR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3102,6 +3102,11 @@
           <t>Price_2026-09-27 13:42</t>
         </is>
       </c>
+      <c r="TR1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-28 16:36</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5785,6 +5790,11 @@
         </is>
       </c>
       <c r="TQ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TR2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8312,6 +8322,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TR3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10875,6 +10890,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TR4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13562,6 +13582,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TR5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16249,6 +16274,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TR6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18936,6 +18966,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="TR7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21623,6 +21658,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TR8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24310,6 +24350,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TR9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26997,6 +27042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TR10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29684,6 +29734,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TR11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32371,6 +32426,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TR12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35058,6 +35118,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TR13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37745,6 +37810,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TR14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40428,6 +40498,11 @@
         </is>
       </c>
       <c r="TQ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TR15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42519,6 +42594,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="TR16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45206,6 +45286,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TR17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47893,6 +47978,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TR18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50580,6 +50670,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TR19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53267,6 +53362,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TR20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -55954,6 +56054,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TR21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58637,6 +58742,11 @@
         </is>
       </c>
       <c r="TQ22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="TR22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -61336,6 +61446,11 @@
         </is>
       </c>
       <c r="TQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TR23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63795,6 +63910,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TR24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TR24"/>
+  <dimension ref="A1:TS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3107,6 +3107,11 @@
           <t>Price_2026-09-28 16:36</t>
         </is>
       </c>
+      <c r="TS1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-29 14:47</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5795,6 +5800,11 @@
         </is>
       </c>
       <c r="TR2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TS2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8327,6 +8337,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TS3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10895,6 +10910,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TS4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13587,6 +13607,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TS5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16279,6 +16304,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TS6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18971,6 +19001,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TS7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21663,6 +21698,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TS8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24355,6 +24395,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TS9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27047,6 +27092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TS10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29739,6 +29789,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TS11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32431,6 +32486,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TS12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35123,6 +35183,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TS13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37815,6 +37880,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TS14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40503,6 +40573,11 @@
         </is>
       </c>
       <c r="TR15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TS15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42599,6 +42674,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TS16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45291,6 +45371,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TS17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47983,6 +48068,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TS18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50675,6 +50765,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TS19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53367,6 +53462,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TS20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56059,6 +56159,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TS21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58749,6 +58854,11 @@
       <c r="TR22" t="inlineStr">
         <is>
           <t>4.299</t>
+        </is>
+      </c>
+      <c r="TS22" t="inlineStr">
+        <is>
+          <t>4.249</t>
         </is>
       </c>
     </row>
@@ -61451,6 +61561,11 @@
         </is>
       </c>
       <c r="TR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TS23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -63915,6 +64030,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TS24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TS24"/>
+  <dimension ref="A1:TT24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3112,6 +3112,11 @@
           <t>Price_2026-09-29 14:47</t>
         </is>
       </c>
+      <c r="TT1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-30 14:46</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5805,6 +5810,11 @@
         </is>
       </c>
       <c r="TS2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TT2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -8342,6 +8352,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TT3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10915,6 +10930,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TT4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13612,6 +13632,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TT5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16309,6 +16334,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TT6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19006,6 +19036,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TT7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21703,6 +21738,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TT8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24400,6 +24440,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TT9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27097,6 +27142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TT10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29794,6 +29844,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TT11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32491,6 +32546,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TT12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35188,6 +35248,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TT13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37885,6 +37950,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TT14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40578,6 +40648,11 @@
         </is>
       </c>
       <c r="TS15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TT15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42679,6 +42754,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TT16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45376,6 +45456,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TT17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48073,6 +48158,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TT18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50770,6 +50860,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TT19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53467,6 +53562,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TT20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56164,6 +56264,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TT21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58859,6 +58964,11 @@
       <c r="TS22" t="inlineStr">
         <is>
           <t>4.249</t>
+        </is>
+      </c>
+      <c r="TT22" t="inlineStr">
+        <is>
+          <t>4.099</t>
         </is>
       </c>
     </row>
@@ -61566,6 +61676,11 @@
         </is>
       </c>
       <c r="TS23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TT23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64035,6 +64150,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TT24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TT24"/>
+  <dimension ref="A1:TU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3117,6 +3117,11 @@
           <t>Price_2026-09-30 14:46</t>
         </is>
       </c>
+      <c r="TU1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-02 14:37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5817,6 +5822,11 @@
       <c r="TT2" t="inlineStr">
         <is>
           <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="TU2" t="inlineStr">
+        <is>
+          <t>$37,200*</t>
         </is>
       </c>
     </row>
@@ -8357,6 +8367,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TU3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10935,6 +10950,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TU4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13637,6 +13657,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TU5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16339,6 +16364,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19041,6 +19071,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TU7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21743,6 +21778,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TU8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24445,6 +24485,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TU9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27147,6 +27192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TU10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29849,6 +29899,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TU11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32551,6 +32606,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TU12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35253,6 +35313,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TU13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -37955,6 +38020,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TU14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40653,6 +40723,11 @@
         </is>
       </c>
       <c r="TT15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TU15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42759,6 +42834,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TU16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45461,6 +45541,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TU17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48163,6 +48248,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TU18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50865,6 +50955,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TU19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53567,6 +53662,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TU20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56269,6 +56369,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TU21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -58969,6 +59074,11 @@
       <c r="TT22" t="inlineStr">
         <is>
           <t>4.099</t>
+        </is>
+      </c>
+      <c r="TU22" t="inlineStr">
+        <is>
+          <t>4.049</t>
         </is>
       </c>
     </row>
@@ -61681,6 +61791,11 @@
         </is>
       </c>
       <c r="TT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TU23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64155,6 +64270,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TU24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TU24"/>
+  <dimension ref="A1:TV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3122,6 +3122,11 @@
           <t>Price_2026-10-02 14:37</t>
         </is>
       </c>
+      <c r="TV1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-03 13:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5825,6 +5830,11 @@
         </is>
       </c>
       <c r="TU2" t="inlineStr">
+        <is>
+          <t>$37,200*</t>
+        </is>
+      </c>
+      <c r="TV2" t="inlineStr">
         <is>
           <t>$37,200*</t>
         </is>
@@ -8372,6 +8382,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10955,6 +10970,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13662,6 +13682,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TV5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16369,6 +16394,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TV6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19076,6 +19106,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21783,6 +21818,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TV8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24490,6 +24530,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27197,6 +27242,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29904,6 +29954,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32611,6 +32666,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TV12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35318,6 +35378,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TV13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38025,6 +38090,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TV14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40728,6 +40798,11 @@
         </is>
       </c>
       <c r="TU15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TV15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42839,6 +42914,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TV16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45546,6 +45626,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TV17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48253,6 +48338,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -50960,6 +51050,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TV19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53667,6 +53762,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TV20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56374,6 +56474,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TV21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59079,6 +59184,11 @@
       <c r="TU22" t="inlineStr">
         <is>
           <t>4.049</t>
+        </is>
+      </c>
+      <c r="TV22" t="inlineStr">
+        <is>
+          <t>3.999</t>
         </is>
       </c>
     </row>
@@ -61796,6 +61906,11 @@
         </is>
       </c>
       <c r="TU23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TV23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64275,6 +64390,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TV24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TV24"/>
+  <dimension ref="A1:TW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3127,6 +3127,11 @@
           <t>Price_2026-10-03 13:12</t>
         </is>
       </c>
+      <c r="TW1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-04 13:50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5835,6 +5840,11 @@
         </is>
       </c>
       <c r="TV2" t="inlineStr">
+        <is>
+          <t>$37,200*</t>
+        </is>
+      </c>
+      <c r="TW2" t="inlineStr">
         <is>
           <t>$37,200*</t>
         </is>
@@ -8387,6 +8397,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10975,6 +10990,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13687,6 +13707,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TW5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16399,6 +16424,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19111,6 +19141,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21823,6 +21858,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TW8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24535,6 +24575,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27247,6 +27292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29959,6 +30009,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32671,6 +32726,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TW12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35383,6 +35443,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TW13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38095,6 +38160,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TW14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40803,6 +40873,11 @@
         </is>
       </c>
       <c r="TV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42919,6 +42994,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TW16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45631,6 +45711,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TW17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48343,6 +48428,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51055,6 +51145,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TW19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53767,6 +53862,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TW20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56479,6 +56579,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TW21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59189,6 +59294,11 @@
       <c r="TV22" t="inlineStr">
         <is>
           <t>3.999</t>
+        </is>
+      </c>
+      <c r="TW22" t="inlineStr">
+        <is>
+          <t>3.949</t>
         </is>
       </c>
     </row>
@@ -61911,6 +62021,11 @@
         </is>
       </c>
       <c r="TV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TW23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64395,6 +64510,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TW24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TW24"/>
+  <dimension ref="A1:TX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3132,6 +3132,11 @@
           <t>Price_2026-10-04 13:50</t>
         </is>
       </c>
+      <c r="TX1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-05 16:57</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5845,6 +5850,11 @@
         </is>
       </c>
       <c r="TW2" t="inlineStr">
+        <is>
+          <t>$37,200*</t>
+        </is>
+      </c>
+      <c r="TX2" t="inlineStr">
         <is>
           <t>$37,200*</t>
         </is>
@@ -8402,6 +8412,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TX3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10995,6 +11010,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TX4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13712,6 +13732,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TX5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16429,6 +16454,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TX6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19146,6 +19176,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TX7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21863,6 +21898,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TX8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24580,6 +24620,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TX9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27297,6 +27342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TX10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30014,6 +30064,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TX11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32731,6 +32786,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TX12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35448,6 +35508,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TX13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38165,6 +38230,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TX14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40878,6 +40948,11 @@
         </is>
       </c>
       <c r="TW15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TX15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -42999,6 +43074,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TX16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45716,6 +45796,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TX17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48433,6 +48518,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TX18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51150,6 +51240,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TX19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53867,6 +53962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TX20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56584,6 +56684,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TX21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59299,6 +59404,11 @@
       <c r="TW22" t="inlineStr">
         <is>
           <t>3.949</t>
+        </is>
+      </c>
+      <c r="TX22" t="inlineStr">
+        <is>
+          <t>4.349</t>
         </is>
       </c>
     </row>
@@ -62026,6 +62136,11 @@
         </is>
       </c>
       <c r="TW23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TX23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64515,6 +64630,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TX24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TX24"/>
+  <dimension ref="A1:TY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3137,6 +3137,11 @@
           <t>Price_2026-10-05 16:57</t>
         </is>
       </c>
+      <c r="TY1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-06 14:54</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3146,7 +3151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SILVERADO</t>
+          <t>NEXT-GENERATION 2027</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5857,6 +5862,11 @@
       <c r="TX2" t="inlineStr">
         <is>
           <t>$37,200*</t>
+        </is>
+      </c>
+      <c r="TY2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -8417,6 +8427,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TY3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11015,6 +11030,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TY4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13737,6 +13757,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TY5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16459,6 +16484,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19181,6 +19211,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TY7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21903,6 +21938,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TY8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24625,6 +24665,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TY9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27347,6 +27392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TY10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30069,6 +30119,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TY11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32791,6 +32846,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TY12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35513,6 +35573,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TY13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38235,6 +38300,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TY14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -40953,6 +41023,11 @@
         </is>
       </c>
       <c r="TX15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TY15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43079,6 +43154,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TY16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45801,6 +45881,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TY17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48523,6 +48608,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TY18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51245,6 +51335,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TY19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -53967,6 +54062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TY20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56689,6 +56789,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TY21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59407,6 +59512,11 @@
         </is>
       </c>
       <c r="TX22" t="inlineStr">
+        <is>
+          <t>4.349</t>
+        </is>
+      </c>
+      <c r="TY22" t="inlineStr">
         <is>
           <t>4.349</t>
         </is>
@@ -62141,6 +62251,11 @@
         </is>
       </c>
       <c r="TX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TY23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64635,6 +64750,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TY24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TY24"/>
+  <dimension ref="A1:TZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3142,6 +3142,11 @@
           <t>Price_2026-10-06 14:54</t>
         </is>
       </c>
+      <c r="TZ1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-08 15:23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5865,6 +5870,11 @@
         </is>
       </c>
       <c r="TY2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TZ2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8432,6 +8442,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TZ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11035,6 +11050,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="TZ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13762,6 +13782,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="TZ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16489,6 +16514,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="TZ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19216,6 +19246,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="TZ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21943,6 +21978,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="TZ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24670,6 +24710,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="TZ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27397,6 +27442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="TZ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30124,6 +30174,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="TZ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32851,6 +32906,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="TZ12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35578,6 +35638,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="TZ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38305,6 +38370,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="TZ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41028,6 +41098,11 @@
         </is>
       </c>
       <c r="TY15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="TZ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43159,6 +43234,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="TZ16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45886,6 +45966,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="TZ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48613,6 +48698,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="TZ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51340,6 +51430,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="TZ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54067,6 +54162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="TZ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56794,6 +56894,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="TZ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59519,6 +59624,11 @@
       <c r="TY22" t="inlineStr">
         <is>
           <t>4.349</t>
+        </is>
+      </c>
+      <c r="TZ22" t="inlineStr">
+        <is>
+          <t>4.299</t>
         </is>
       </c>
     </row>
@@ -62256,6 +62366,11 @@
         </is>
       </c>
       <c r="TY23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="TZ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64755,6 +64870,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="TZ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:TZ24"/>
+  <dimension ref="A1:UA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3147,6 +3147,11 @@
           <t>Price_2026-10-08 15:23</t>
         </is>
       </c>
+      <c r="UA1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-09 15:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5875,6 +5880,11 @@
         </is>
       </c>
       <c r="TZ2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UA2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8447,6 +8457,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UA3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11055,6 +11070,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UA4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13787,6 +13807,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="UA5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16519,6 +16544,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19251,6 +19281,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UA7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21983,6 +22018,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="UA8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24715,6 +24755,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UA9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27447,6 +27492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UA10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30179,6 +30229,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UA11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32911,6 +32966,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UA12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35643,6 +35703,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UA13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38375,6 +38440,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UA14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41103,6 +41173,11 @@
         </is>
       </c>
       <c r="TZ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UA15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43239,6 +43314,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UA16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45971,6 +46051,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UA17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48703,6 +48788,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UA18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51435,6 +51525,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UA19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54167,6 +54262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UA20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -56899,6 +56999,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="UA21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59627,6 +59732,11 @@
         </is>
       </c>
       <c r="TZ22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="UA22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -62371,6 +62481,11 @@
         </is>
       </c>
       <c r="TZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UA23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64875,6 +64990,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="UA24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UA24"/>
+  <dimension ref="A1:UB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3152,6 +3152,11 @@
           <t>Price_2026-10-09 15:08</t>
         </is>
       </c>
+      <c r="UB1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-10 14:24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5885,6 +5890,11 @@
         </is>
       </c>
       <c r="UA2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UB2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8462,6 +8472,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UB3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11075,6 +11090,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UB4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13812,6 +13832,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="UB5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16549,6 +16574,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UB6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19286,6 +19316,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UB7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22023,6 +22058,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="UB8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24760,6 +24800,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UB9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27497,6 +27542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UB10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30234,6 +30284,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UB11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32971,6 +33026,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UB12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35708,6 +35768,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UB13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38445,6 +38510,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UB14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41178,6 +41248,11 @@
         </is>
       </c>
       <c r="UA15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UB15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43319,6 +43394,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UB16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46056,6 +46136,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UB17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48793,6 +48878,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UB18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51530,6 +51620,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UB19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54267,6 +54362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UB20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57004,6 +57104,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="UB21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59737,6 +59842,11 @@
         </is>
       </c>
       <c r="UA22" t="inlineStr">
+        <is>
+          <t>4.299</t>
+        </is>
+      </c>
+      <c r="UB22" t="inlineStr">
         <is>
           <t>4.299</t>
         </is>
@@ -62486,6 +62596,11 @@
         </is>
       </c>
       <c r="UA23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UB23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -64995,6 +65110,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UB24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UB24"/>
+  <dimension ref="A1:UC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3157,6 +3157,11 @@
           <t>Price_2026-10-10 14:24</t>
         </is>
       </c>
+      <c r="UC1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-11 14:48</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5895,6 +5900,11 @@
         </is>
       </c>
       <c r="UB2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UC2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8477,6 +8487,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UC3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11095,6 +11110,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UC4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13837,6 +13857,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="UC5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16579,6 +16604,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19321,6 +19351,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UC7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22063,6 +22098,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="UC8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24805,6 +24845,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UC9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27547,6 +27592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UC10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30289,6 +30339,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UC11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33031,6 +33086,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UC12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35773,6 +35833,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UC13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38515,6 +38580,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UC14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41253,6 +41323,11 @@
         </is>
       </c>
       <c r="UB15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UC15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43399,6 +43474,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UC16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46141,6 +46221,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UC17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48883,6 +48968,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UC18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51625,6 +51715,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UC19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54367,6 +54462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UC20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57109,6 +57209,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="UC21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59849,6 +59954,11 @@
       <c r="UB22" t="inlineStr">
         <is>
           <t>4.299</t>
+        </is>
+      </c>
+      <c r="UC22" t="inlineStr">
+        <is>
+          <t>4.159</t>
         </is>
       </c>
     </row>
@@ -62601,6 +62711,11 @@
         </is>
       </c>
       <c r="UB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UC23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65115,6 +65230,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UC24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UC24"/>
+  <dimension ref="A1:UD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3162,6 +3162,11 @@
           <t>Price_2026-10-11 14:48</t>
         </is>
       </c>
+      <c r="UD1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-12 17:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5905,6 +5910,11 @@
         </is>
       </c>
       <c r="UC2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UD2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8492,6 +8502,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UD3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11115,6 +11130,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UD4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13862,6 +13882,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="UD5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16609,6 +16634,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UD6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19356,6 +19386,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UD7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22103,6 +22138,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="UD8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24850,6 +24890,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UD9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27597,6 +27642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UD10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30344,6 +30394,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UD11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33091,6 +33146,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UD12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35838,6 +35898,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UD13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38585,6 +38650,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UD14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41328,6 +41398,11 @@
         </is>
       </c>
       <c r="UC15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UD15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43479,6 +43554,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UD16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46226,6 +46306,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UD17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -48973,6 +49058,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UD18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51720,6 +51810,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UD19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54467,6 +54562,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UD20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57214,6 +57314,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="UD21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -59959,6 +60064,11 @@
       <c r="UC22" t="inlineStr">
         <is>
           <t>4.159</t>
+        </is>
+      </c>
+      <c r="UD22" t="inlineStr">
+        <is>
+          <t>4.149</t>
         </is>
       </c>
     </row>
@@ -62716,6 +62826,11 @@
         </is>
       </c>
       <c r="UC23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UD23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65235,6 +65350,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UD24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UD24"/>
+  <dimension ref="A1:UE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3167,6 +3167,11 @@
           <t>Price_2026-10-12 17:30</t>
         </is>
       </c>
+      <c r="UE1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-13 15:44</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5915,6 +5920,11 @@
         </is>
       </c>
       <c r="UD2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UE2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8507,6 +8517,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UE3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11135,6 +11150,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UE4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13887,6 +13907,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UE5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16639,6 +16664,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19391,6 +19421,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UE7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22143,6 +22178,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="UE8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24895,6 +24935,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UE9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27647,6 +27692,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UE10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30399,6 +30449,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UE11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33151,6 +33206,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UE12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35903,6 +35963,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UE13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38655,6 +38720,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UE14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41405,6 +41475,11 @@
       <c r="UD15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UE15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -43559,6 +43634,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UE16" t="inlineStr">
+        <is>
+          <t>$14.86</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46311,6 +46391,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UE17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49063,6 +49148,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UE18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51815,6 +51905,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UE19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54567,6 +54662,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UE20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57319,6 +57419,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="UE21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60069,6 +60174,11 @@
       <c r="UD22" t="inlineStr">
         <is>
           <t>4.149</t>
+        </is>
+      </c>
+      <c r="UE22" t="inlineStr">
+        <is>
+          <t>4.099</t>
         </is>
       </c>
     </row>
@@ -62831,6 +62941,11 @@
         </is>
       </c>
       <c r="UD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UE23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65355,6 +65470,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UE24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UE24"/>
+  <dimension ref="A1:UF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3172,6 +3172,11 @@
           <t>Price_2026-10-13 15:44</t>
         </is>
       </c>
+      <c r="UF1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-14 13:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5925,6 +5930,11 @@
         </is>
       </c>
       <c r="UE2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UF2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8522,6 +8532,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UF3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11155,6 +11170,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UF4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13912,6 +13932,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UF5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16669,6 +16694,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UF6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19426,6 +19456,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UF7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22183,6 +22218,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UF8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24940,6 +24980,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="UF9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27697,6 +27742,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="UF10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30454,6 +30504,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="UF11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33211,6 +33266,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UF12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35968,6 +36028,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="UF13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38725,6 +38790,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UF14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41480,6 +41550,11 @@
       <c r="UE15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="UF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -43639,6 +43714,11 @@
           <t>$14.86</t>
         </is>
       </c>
+      <c r="UF16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46396,6 +46476,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UF17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49153,6 +49238,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UF18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51910,6 +52000,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UF19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54667,6 +54762,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UF20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57424,6 +57524,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UF21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60177,6 +60282,11 @@
         </is>
       </c>
       <c r="UE22" t="inlineStr">
+        <is>
+          <t>4.099</t>
+        </is>
+      </c>
+      <c r="UF22" t="inlineStr">
         <is>
           <t>4.099</t>
         </is>
@@ -62946,6 +63056,11 @@
         </is>
       </c>
       <c r="UE23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UF23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65475,6 +65590,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UF24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UF24"/>
+  <dimension ref="A1:UG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3177,11 @@
           <t>Price_2026-10-14 13:29</t>
         </is>
       </c>
+      <c r="UG1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-15 13:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5935,6 +5940,11 @@
         </is>
       </c>
       <c r="UF2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UG2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8537,6 +8547,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UG3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11175,6 +11190,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UG4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13937,6 +13957,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UG5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16699,6 +16724,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19461,6 +19491,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UG7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22223,6 +22258,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UG8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24985,6 +25025,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UG9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27747,6 +27792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UG10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30509,6 +30559,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UG11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33271,6 +33326,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UG12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36033,6 +36093,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UG13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38795,6 +38860,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UG14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41553,6 +41623,11 @@
         </is>
       </c>
       <c r="UF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UG15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43719,6 +43794,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UG16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46481,6 +46561,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UG17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49243,6 +49328,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UG18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52005,6 +52095,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UG19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54767,6 +54862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UG20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57529,6 +57629,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="UG21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60289,6 +60394,11 @@
       <c r="UF22" t="inlineStr">
         <is>
           <t>4.099</t>
+        </is>
+      </c>
+      <c r="UG22" t="inlineStr">
+        <is>
+          <t>3.999</t>
         </is>
       </c>
     </row>
@@ -63061,6 +63171,11 @@
         </is>
       </c>
       <c r="UF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UG23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65595,6 +65710,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UG24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UG24"/>
+  <dimension ref="A1:UH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3182,6 +3182,11 @@
           <t>Price_2026-10-15 13:15</t>
         </is>
       </c>
+      <c r="UH1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-16 13:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5945,6 +5950,11 @@
         </is>
       </c>
       <c r="UG2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UH2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8552,6 +8562,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UH3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11195,6 +11210,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UH4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13962,6 +13982,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UH5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16729,6 +16754,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UH6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19496,6 +19526,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UH7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22263,6 +22298,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UH8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25030,6 +25070,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UH9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27797,6 +27842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UH10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30564,6 +30614,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UH11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33331,6 +33386,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UH12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36098,6 +36158,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UH13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38865,6 +38930,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UH14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41630,6 +41700,11 @@
       <c r="UG15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UH15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -43799,6 +43874,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UH16" t="inlineStr">
+        <is>
+          <t>$14.86</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46566,6 +46646,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UH17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49333,6 +49418,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UH18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52100,6 +52190,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UH19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54867,6 +54962,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UH20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57634,6 +57734,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UH21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60397,6 +60502,11 @@
         </is>
       </c>
       <c r="UG22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="UH22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -63176,6 +63286,11 @@
         </is>
       </c>
       <c r="UG23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UH23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65715,6 +65830,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UH24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UH24"/>
+  <dimension ref="A1:UI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3187,6 +3187,11 @@
           <t>Price_2026-10-16 13:11</t>
         </is>
       </c>
+      <c r="UI1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-17 12:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5955,6 +5960,11 @@
         </is>
       </c>
       <c r="UH2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UI2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8567,6 +8577,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UI3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11215,6 +11230,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UI4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13987,6 +14007,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UI5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16759,6 +16784,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19531,6 +19561,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UI7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22303,6 +22338,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UI8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25075,6 +25115,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="UI9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27847,6 +27892,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="UI10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30619,6 +30669,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="UI11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33391,6 +33446,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UI12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36163,6 +36223,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="UI13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38935,6 +39000,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UI14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41705,6 +41775,11 @@
       <c r="UH15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="UI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -43879,6 +43954,11 @@
           <t>$14.86</t>
         </is>
       </c>
+      <c r="UI16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46651,6 +46731,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UI17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49423,6 +49508,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UI18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52195,6 +52285,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UI19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -54967,6 +55062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UI20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57739,6 +57839,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UI21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60507,6 +60612,11 @@
         </is>
       </c>
       <c r="UH22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="UI22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -63291,6 +63401,11 @@
         </is>
       </c>
       <c r="UH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UI23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65835,6 +65950,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UI24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UI24"/>
+  <dimension ref="A1:UJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,6 +3192,11 @@
           <t>Price_2026-10-17 12:09</t>
         </is>
       </c>
+      <c r="UJ1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-18 12:37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5965,6 +5970,11 @@
         </is>
       </c>
       <c r="UI2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UJ2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8582,6 +8592,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UJ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11235,6 +11250,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UJ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14012,6 +14032,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UJ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16789,6 +16814,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UJ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19566,6 +19596,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UJ7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22343,6 +22378,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UJ8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25120,6 +25160,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UJ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27897,6 +27942,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UJ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30674,6 +30724,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UJ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33451,6 +33506,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UJ12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36228,6 +36288,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UJ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39005,6 +39070,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UJ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41778,6 +41848,11 @@
         </is>
       </c>
       <c r="UI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -43959,6 +44034,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UJ16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46736,6 +46816,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UJ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49513,6 +49598,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UJ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52290,6 +52380,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UJ19" t="inlineStr">
+        <is>
+          <t>$1.98</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55067,6 +55162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UJ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57844,6 +57944,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UJ21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60617,6 +60722,11 @@
         </is>
       </c>
       <c r="UI22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="UJ22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -63406,6 +63516,11 @@
         </is>
       </c>
       <c r="UI23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UJ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -65955,6 +66070,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UJ24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UJ24"/>
+  <dimension ref="A1:UK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3197,6 +3197,11 @@
           <t>Price_2026-10-18 12:37</t>
         </is>
       </c>
+      <c r="UK1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-19 15:27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5975,6 +5980,11 @@
         </is>
       </c>
       <c r="UJ2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UK2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8597,6 +8607,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UK3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11255,6 +11270,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UK4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14037,6 +14057,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UK5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16819,6 +16844,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19601,6 +19631,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="UK7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22383,6 +22418,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UK8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25165,6 +25205,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UK9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27947,6 +27992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UK10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30729,6 +30779,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UK11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33511,6 +33566,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UK12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36293,6 +36353,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UK13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39075,6 +39140,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UK14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41855,6 +41925,11 @@
       <c r="UJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UK15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -44039,6 +44114,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UK16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46821,6 +46901,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UK17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49603,6 +49688,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UK18" t="inlineStr">
+        <is>
+          <t>$0.48</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52385,6 +52475,11 @@
           <t>$1.98</t>
         </is>
       </c>
+      <c r="UK19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55167,6 +55262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UK20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -57949,6 +58049,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UK21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60729,6 +60834,11 @@
       <c r="UJ22" t="inlineStr">
         <is>
           <t>3.999</t>
+        </is>
+      </c>
+      <c r="UK22" t="inlineStr">
+        <is>
+          <t>3.979</t>
         </is>
       </c>
     </row>
@@ -63521,6 +63631,11 @@
         </is>
       </c>
       <c r="UJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UK23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66075,6 +66190,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UK24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UK24"/>
+  <dimension ref="A1:UL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3202,6 +3202,11 @@
           <t>Price_2026-10-19 15:27</t>
         </is>
       </c>
+      <c r="UL1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-20 13:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5985,6 +5990,11 @@
         </is>
       </c>
       <c r="UK2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UL2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8612,6 +8622,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UL3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11275,6 +11290,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UL4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14062,6 +14082,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UL5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16849,6 +16874,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UL6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19636,6 +19666,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="UL7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22423,6 +22458,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UL8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25210,6 +25250,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="UL9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27997,6 +28042,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="UL10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30784,6 +30834,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="UL11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33571,6 +33626,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UL12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36358,6 +36418,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="UL13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39145,6 +39210,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UL14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41930,6 +42000,11 @@
       <c r="UK15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="UL15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -44119,6 +44194,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UL16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46906,6 +46986,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UL17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46915,7 +47000,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fresh Chiquita Bananas</t>
+          <t>Fresh Bananas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -49691,6 +49776,11 @@
       <c r="UK18" t="inlineStr">
         <is>
           <t>$0.48</t>
+        </is>
+      </c>
+      <c r="UL18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
         </is>
       </c>
     </row>
@@ -52480,6 +52570,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UL19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55267,6 +55362,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UL20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58054,6 +58154,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UL21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60837,6 +60942,11 @@
         </is>
       </c>
       <c r="UK22" t="inlineStr">
+        <is>
+          <t>3.979</t>
+        </is>
+      </c>
+      <c r="UL22" t="inlineStr">
         <is>
           <t>3.979</t>
         </is>
@@ -63636,6 +63746,11 @@
         </is>
       </c>
       <c r="UK23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UL23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66195,6 +66310,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UL24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UL24"/>
+  <dimension ref="A1:UM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3207,6 +3207,11 @@
           <t>Price_2026-10-20 13:29</t>
         </is>
       </c>
+      <c r="UM1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-21 13:36</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5995,6 +6000,11 @@
         </is>
       </c>
       <c r="UL2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UM2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8627,6 +8637,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UM3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11295,6 +11310,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UM4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14087,6 +14107,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UM5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16879,6 +16904,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19671,6 +19701,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UM7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22463,6 +22498,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UM8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25255,6 +25295,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UM9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28047,6 +28092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UM10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30839,6 +30889,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UM11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33631,6 +33686,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UM12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36423,6 +36483,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UM13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39215,6 +39280,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UM14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42003,6 +42073,11 @@
         </is>
       </c>
       <c r="UL15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UM15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44199,6 +44274,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UM16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46991,6 +47071,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UM17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49783,6 +49868,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UM18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52575,6 +52665,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UM19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55367,6 +55462,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UM20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58159,6 +58259,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UM21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -60949,6 +61054,11 @@
       <c r="UL22" t="inlineStr">
         <is>
           <t>3.979</t>
+        </is>
+      </c>
+      <c r="UM22" t="inlineStr">
+        <is>
+          <t>3.959</t>
         </is>
       </c>
     </row>
@@ -63751,6 +63861,11 @@
         </is>
       </c>
       <c r="UL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UM23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66315,6 +66430,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UM24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UM24"/>
+  <dimension ref="A1:UN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3212,6 +3212,11 @@
           <t>Price_2026-10-21 13:36</t>
         </is>
       </c>
+      <c r="UN1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-22 13:37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6005,6 +6010,11 @@
         </is>
       </c>
       <c r="UM2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UN2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8642,6 +8652,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UN3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11315,6 +11330,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UN4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14112,6 +14132,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UN5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16909,6 +16934,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UN6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19706,6 +19736,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UN7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22503,6 +22538,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UN8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25300,6 +25340,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UN9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28097,6 +28142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UN10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30894,6 +30944,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UN11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33691,6 +33746,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UN12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36488,6 +36548,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UN13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39285,6 +39350,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UN14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42078,6 +42148,11 @@
         </is>
       </c>
       <c r="UM15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UN15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44279,6 +44354,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UN16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47076,6 +47156,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UN17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49873,6 +49958,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UN18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52670,6 +52760,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UN19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55467,6 +55562,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UN20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58264,6 +58364,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UN21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61059,6 +61164,11 @@
       <c r="UM22" t="inlineStr">
         <is>
           <t>3.959</t>
+        </is>
+      </c>
+      <c r="UN22" t="inlineStr">
+        <is>
+          <t>4.199</t>
         </is>
       </c>
     </row>
@@ -63866,6 +63976,11 @@
         </is>
       </c>
       <c r="UM23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UN23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66435,6 +66550,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UN24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UN24"/>
+  <dimension ref="A1:UO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3217,6 +3217,11 @@
           <t>Price_2026-10-22 13:37</t>
         </is>
       </c>
+      <c r="UO1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-23 13:14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6015,6 +6020,11 @@
         </is>
       </c>
       <c r="UN2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UO2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8657,6 +8667,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UO3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11335,6 +11350,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UO4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14137,6 +14157,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UO5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16939,6 +16964,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19741,6 +19771,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UO7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22543,6 +22578,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UO8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25345,6 +25385,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UO9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28147,6 +28192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UO10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -30949,6 +30999,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UO11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33751,6 +33806,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UO12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36553,6 +36613,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UO13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39355,6 +39420,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UO14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42155,6 +42225,11 @@
       <c r="UN15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UO15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -44359,6 +44434,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UO16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47161,6 +47241,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UO17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -49963,6 +50048,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UO18" t="inlineStr">
+        <is>
+          <t>$0.48</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52765,6 +52855,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UO19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55567,6 +55662,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UO20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58369,6 +58469,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UO21" t="inlineStr">
+        <is>
+          <t>$1.49</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61167,6 +61272,11 @@
         </is>
       </c>
       <c r="UN22" t="inlineStr">
+        <is>
+          <t>4.199</t>
+        </is>
+      </c>
+      <c r="UO22" t="inlineStr">
         <is>
           <t>4.199</t>
         </is>
@@ -63981,6 +64091,11 @@
         </is>
       </c>
       <c r="UN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UO23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66555,6 +66670,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UO24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UO24"/>
+  <dimension ref="A1:UP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,6 +3222,11 @@
           <t>Price_2026-10-23 13:14</t>
         </is>
       </c>
+      <c r="UP1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-24 12:38</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6025,6 +6030,11 @@
         </is>
       </c>
       <c r="UO2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UP2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8672,6 +8682,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UP3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11355,6 +11370,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UP4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14162,6 +14182,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UP5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16969,6 +16994,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UP6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19776,6 +19806,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="UP7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22583,6 +22618,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UP8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25390,6 +25430,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="UP9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28197,6 +28242,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="UP10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31004,6 +31054,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="UP11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33811,6 +33866,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UP12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36618,6 +36678,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="UP13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39425,6 +39490,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UP14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42230,6 +42300,11 @@
       <c r="UO15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="UP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -44439,6 +44514,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UP16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47246,6 +47326,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UP17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50053,6 +50138,11 @@
           <t>$0.48</t>
         </is>
       </c>
+      <c r="UP18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52860,6 +52950,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UP19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55667,6 +55762,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UP20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58474,6 +58574,11 @@
           <t>$1.49</t>
         </is>
       </c>
+      <c r="UP21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61279,6 +61384,11 @@
       <c r="UO22" t="inlineStr">
         <is>
           <t>4.199</t>
+        </is>
+      </c>
+      <c r="UP22" t="inlineStr">
+        <is>
+          <t>4.099</t>
         </is>
       </c>
     </row>
@@ -64096,6 +64206,11 @@
         </is>
       </c>
       <c r="UO23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UP23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66675,6 +66790,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UP24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UP24"/>
+  <dimension ref="A1:UQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3227,6 +3227,11 @@
           <t>Price_2026-10-24 12:38</t>
         </is>
       </c>
+      <c r="UQ1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-25 13:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6035,6 +6040,11 @@
         </is>
       </c>
       <c r="UP2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UQ2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8687,6 +8697,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UQ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11375,6 +11390,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UQ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14187,6 +14207,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UQ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16999,6 +17024,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19811,6 +19841,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UQ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22623,6 +22658,11 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="UQ8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25435,6 +25475,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UQ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28247,6 +28292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UQ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31059,6 +31109,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UQ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33871,6 +33926,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UQ12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36683,6 +36743,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UQ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39495,6 +39560,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UQ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42303,6 +42373,11 @@
         </is>
       </c>
       <c r="UP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UQ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44519,6 +44594,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UQ16" t="inlineStr">
+        <is>
+          <t>$12.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47331,6 +47411,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UQ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50143,6 +50228,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UQ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52955,6 +53045,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UQ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55767,6 +55862,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UQ20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58579,6 +58679,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UQ21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61387,6 +61492,11 @@
         </is>
       </c>
       <c r="UP22" t="inlineStr">
+        <is>
+          <t>4.099</t>
+        </is>
+      </c>
+      <c r="UQ22" t="inlineStr">
         <is>
           <t>4.099</t>
         </is>
@@ -64211,6 +64321,11 @@
         </is>
       </c>
       <c r="UP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UQ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66795,6 +66910,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UQ24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UQ24"/>
+  <dimension ref="A1:UR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3232,6 +3232,11 @@
           <t>Price_2026-10-25 13:08</t>
         </is>
       </c>
+      <c r="UR1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-26 15:01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6045,6 +6050,11 @@
         </is>
       </c>
       <c r="UQ2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UR2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8702,6 +8712,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UR3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11395,6 +11410,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UR4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14212,6 +14232,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UR5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17029,6 +17054,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UR6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19846,6 +19876,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UR7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22663,6 +22698,11 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="UR8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25480,6 +25520,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UR9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28297,6 +28342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UR10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31114,6 +31164,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UR11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33931,6 +33986,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UR12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36748,6 +36808,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UR13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39565,6 +39630,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="UR14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42378,6 +42448,11 @@
         </is>
       </c>
       <c r="UQ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UR15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44599,6 +44674,11 @@
           <t>$12.96</t>
         </is>
       </c>
+      <c r="UR16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47416,6 +47496,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UR17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50233,6 +50318,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UR18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53050,6 +53140,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UR19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55867,6 +55962,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UR20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58684,6 +58784,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UR21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61497,6 +61602,11 @@
         </is>
       </c>
       <c r="UQ22" t="inlineStr">
+        <is>
+          <t>4.099</t>
+        </is>
+      </c>
+      <c r="UR22" t="inlineStr">
         <is>
           <t>4.099</t>
         </is>
@@ -64326,6 +64436,11 @@
         </is>
       </c>
       <c r="UQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UR23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -66915,6 +67030,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UR24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UR24"/>
+  <dimension ref="A1:US24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3237,6 +3237,11 @@
           <t>Price_2026-10-26 15:01</t>
         </is>
       </c>
+      <c r="US1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-27 14:06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6055,6 +6060,11 @@
         </is>
       </c>
       <c r="UR2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="US2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8717,6 +8727,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="US3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11415,6 +11430,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="US4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14237,6 +14257,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="US5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17059,6 +17084,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="US6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19881,6 +19911,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="US7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22703,6 +22738,11 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="US8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25525,6 +25565,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="US9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28347,6 +28392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="US10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31169,6 +31219,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="US11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -33991,6 +34046,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="US12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36813,6 +36873,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="US13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39635,6 +39700,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="US14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42455,6 +42525,11 @@
       <c r="UR15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="US15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -44679,6 +44754,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="US16" t="inlineStr">
+        <is>
+          <t>$14.86</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47501,6 +47581,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="US17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50323,6 +50408,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="US18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53145,6 +53235,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="US19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -55967,6 +56062,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="US20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58789,6 +58889,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="US21" t="inlineStr">
+        <is>
+          <t>$1.49</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61609,6 +61714,11 @@
       <c r="UR22" t="inlineStr">
         <is>
           <t>4.099</t>
+        </is>
+      </c>
+      <c r="US22" t="inlineStr">
+        <is>
+          <t>3.939</t>
         </is>
       </c>
     </row>
@@ -64441,6 +64551,11 @@
         </is>
       </c>
       <c r="UR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="US23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -67035,6 +67150,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="US24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:US24"/>
+  <dimension ref="A1:UT24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3242,6 +3242,11 @@
           <t>Price_2026-10-27 14:06</t>
         </is>
       </c>
+      <c r="UT1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-28 15:01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6065,6 +6070,11 @@
         </is>
       </c>
       <c r="US2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UT2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8732,6 +8742,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UT3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11435,6 +11450,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UT4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14262,6 +14282,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UT5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17089,6 +17114,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UT6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19916,6 +19946,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="UT7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22743,6 +22778,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="UT8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25570,6 +25610,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="UT9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28397,6 +28442,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="UT10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31224,6 +31274,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="UT11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34051,6 +34106,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UT12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36878,6 +36938,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="UT13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39705,6 +39770,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UT14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42530,6 +42600,11 @@
       <c r="US15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="UT15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -44759,6 +44834,11 @@
           <t>$14.86</t>
         </is>
       </c>
+      <c r="UT16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47586,6 +47666,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UT17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50413,6 +50498,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UT18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53240,6 +53330,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UT19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -56067,6 +56162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="UT20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58894,6 +58994,11 @@
           <t>$1.49</t>
         </is>
       </c>
+      <c r="UT21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61717,6 +61822,11 @@
         </is>
       </c>
       <c r="US22" t="inlineStr">
+        <is>
+          <t>3.939</t>
+        </is>
+      </c>
+      <c r="UT22" t="inlineStr">
         <is>
           <t>3.939</t>
         </is>
@@ -64556,6 +64666,11 @@
         </is>
       </c>
       <c r="US23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UT23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -67155,6 +67270,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UT24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UT24"/>
+  <dimension ref="A1:UU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3247,6 +3247,11 @@
           <t>Price_2026-10-28 15:01</t>
         </is>
       </c>
+      <c r="UU1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-29 15:07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6075,6 +6080,11 @@
         </is>
       </c>
       <c r="UT2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UU2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8747,6 +8757,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UU3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11455,6 +11470,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UU4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14287,6 +14307,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UU5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17119,6 +17144,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19951,6 +19981,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UU7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22783,6 +22818,11 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="UU8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25615,6 +25655,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UU9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28447,6 +28492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UU10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31279,6 +31329,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UU11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34111,6 +34166,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UU12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36943,6 +37003,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UU13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39775,6 +39840,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UU14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42603,6 +42673,11 @@
         </is>
       </c>
       <c r="UT15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UU15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44839,6 +44914,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UU16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47671,6 +47751,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UU17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50503,6 +50588,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UU18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53335,6 +53425,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UU19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -56167,6 +56262,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UU20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -58999,6 +59099,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UU21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61829,6 +61934,11 @@
       <c r="UT22" t="inlineStr">
         <is>
           <t>3.939</t>
+        </is>
+      </c>
+      <c r="UU22" t="inlineStr">
+        <is>
+          <t>3.899</t>
         </is>
       </c>
     </row>
@@ -64671,6 +64781,11 @@
         </is>
       </c>
       <c r="UT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UU23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -67275,6 +67390,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UU24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UU24"/>
+  <dimension ref="A1:UV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3252,6 +3252,11 @@
           <t>Price_2026-10-29 15:07</t>
         </is>
       </c>
+      <c r="UV1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-30 15:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6085,6 +6090,11 @@
         </is>
       </c>
       <c r="UU2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UV2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8762,6 +8772,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11475,6 +11490,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14312,6 +14332,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UV5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17149,6 +17174,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UV6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19986,6 +20016,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22823,6 +22858,11 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="UV8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25660,6 +25700,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28497,6 +28542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31334,6 +31384,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34171,6 +34226,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UV12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37008,6 +37068,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UV13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39845,6 +39910,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UV14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42678,6 +42748,11 @@
         </is>
       </c>
       <c r="UU15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UV15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44919,6 +44994,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UV16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47756,6 +47836,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UV17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50593,6 +50678,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53430,6 +53520,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UV19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -56267,6 +56362,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UV20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -59104,6 +59204,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UV21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -61937,6 +62042,11 @@
         </is>
       </c>
       <c r="UU22" t="inlineStr">
+        <is>
+          <t>3.899</t>
+        </is>
+      </c>
+      <c r="UV22" t="inlineStr">
         <is>
           <t>3.899</t>
         </is>
@@ -64786,6 +64896,11 @@
         </is>
       </c>
       <c r="UU23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UV23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -67395,6 +67510,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UV24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:UV24"/>
+  <dimension ref="A1:UW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,6 +3257,11 @@
           <t>Price_2026-10-30 15:00</t>
         </is>
       </c>
+      <c r="UW1" t="inlineStr">
+        <is>
+          <t>Price_2026-10-31 14:28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6095,6 +6100,11 @@
         </is>
       </c>
       <c r="UV2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UW2" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -8777,6 +8787,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11495,6 +11510,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="UW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14337,6 +14357,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="UW5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17179,6 +17204,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20021,6 +20051,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22863,6 +22898,11 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="UW8" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25705,6 +25745,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="UW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28547,6 +28592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="UW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31389,6 +31439,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="UW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -34231,6 +34286,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UW12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -37073,6 +37133,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="UW13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39915,6 +39980,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="UW14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42753,6 +42823,11 @@
         </is>
       </c>
       <c r="UV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="UW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -44999,6 +45074,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="UW16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47841,6 +47921,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="UW17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -50683,6 +50768,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="UW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -53525,6 +53615,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="UW19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -56367,6 +56462,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="UW20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -59209,6 +59309,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="UW21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -62047,6 +62152,11 @@
         </is>
       </c>
       <c r="UV22" t="inlineStr">
+        <is>
+          <t>3.899</t>
+        </is>
+      </c>
+      <c r="UW22" t="inlineStr">
         <is>
           <t>3.899</t>
         </is>
@@ -64901,6 +65011,11 @@
         </is>
       </c>
       <c r="UV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="UW23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -67515,6 +67630,11 @@
           <t>Error: Anomaly</t>
         </is>
       </c>
+      <c r="UW24" t="inlineStr">
+        <is>
+          <t>Error: Anomaly</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
